--- a/artfynd/A 53909-2023 artfynd.xlsx
+++ b/artfynd/A 53909-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135707222</v>
       </c>
       <c r="B2" t="n">
-        <v>99312</v>
+        <v>99314</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53909-2023 artfynd.xlsx
+++ b/artfynd/A 53909-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135707222</v>
       </c>
       <c r="B2" t="n">
-        <v>99314</v>
+        <v>99331</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53909-2023 artfynd.xlsx
+++ b/artfynd/A 53909-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135707222</v>
       </c>
       <c r="B2" t="n">
-        <v>99331</v>
+        <v>99332</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53909-2023 artfynd.xlsx
+++ b/artfynd/A 53909-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135707222</v>
       </c>
       <c r="B2" t="n">
-        <v>99332</v>
+        <v>99333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53909-2023 artfynd.xlsx
+++ b/artfynd/A 53909-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135707222</v>
       </c>
       <c r="B2" t="n">
-        <v>99333</v>
+        <v>99334</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53909-2023 artfynd.xlsx
+++ b/artfynd/A 53909-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135707222</v>
       </c>
       <c r="B2" t="n">
-        <v>99334</v>
+        <v>99340</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53909-2023 artfynd.xlsx
+++ b/artfynd/A 53909-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135707222</v>
       </c>
       <c r="B2" t="n">
-        <v>99340</v>
+        <v>99341</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53909-2023 artfynd.xlsx
+++ b/artfynd/A 53909-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135707222</v>
       </c>
       <c r="B2" t="n">
-        <v>99341</v>
+        <v>99352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
